--- a/Excel/CardSpecialConfig.xlsx
+++ b/Excel/CardSpecialConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="29">
   <si>
     <t>#</t>
   </si>
@@ -93,6 +98,27 @@
   </si>
   <si>
     <t>2001,2002,2003,2010</t>
+  </si>
+  <si>
+    <t>神鉴青龙</t>
+  </si>
+  <si>
+    <t>2001,2003,2010,2012,2013</t>
+  </si>
+  <si>
+    <t>1,2,1,2,1</t>
+  </si>
+  <si>
+    <t>神鉴白虎</t>
+  </si>
+  <si>
+    <t>神鉴朱雀</t>
+  </si>
+  <si>
+    <t>神鉴玄武</t>
+  </si>
+  <si>
+    <t>神鉴麒麟</t>
   </si>
 </sst>
 </file>
@@ -1092,25 +1118,25 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="9.75221238938053" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6283185840708" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.3716814159292" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.7522123893805" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.2477876106195" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.25" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="10:10">
+    <row r="1" customHeight="1" spans="3:13">
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="10:10">
+    <row r="2" customHeight="1" spans="3:13">
       <c r="J2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1133,7 +1159,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1156,7 +1182,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1302,7 +1328,7 @@
       <c r="L10" s="2"/>
       <c r="M10" s="5"/>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="4:13">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="D11" s="2"/>
       <c r="E11" s="5"/>
       <c r="F11" s="1"/>
@@ -1312,55 +1338,132 @@
       <c r="L11" s="2"/>
       <c r="M11" s="5"/>
     </row>
-    <row r="12" customHeight="1" spans="4:13">
-      <c r="D12" s="2"/>
-      <c r="E12" s="5"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+    <row r="12" customHeight="1" spans="3:13">
+      <c r="C12" s="1">
+        <v>6</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1998006</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="L12" s="2"/>
       <c r="M12" s="5"/>
     </row>
-    <row r="13" customHeight="1" spans="4:13">
-      <c r="D13" s="2"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+    <row r="13" customHeight="1" spans="3:13">
+      <c r="C13" s="1">
+        <v>7</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1998007</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="5"/>
     </row>
-    <row r="14" customHeight="1" spans="4:13">
-      <c r="D14" s="2"/>
-      <c r="E14" s="5"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+    <row r="14" customHeight="1" spans="3:13">
+      <c r="C14" s="1">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4">
+        <v>1998008</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="L14" s="2"/>
       <c r="M14" s="5"/>
     </row>
-    <row r="15" customHeight="1" spans="4:13">
-      <c r="D15" s="2"/>
-      <c r="E15" s="5"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
+    <row r="15" customHeight="1" spans="3:13">
+      <c r="C15" s="1">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1998009</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="5"/>
     </row>
     <row r="16" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+      <c r="C16" s="1">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1998010</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="L16" s="2"/>
       <c r="M16" s="5"/>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="5:13">
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="E17" s="5"/>
       <c r="F17" s="1"/>
       <c r="G17" s="2"/>
@@ -1380,7 +1483,7 @@
       <c r="L18" s="2"/>
       <c r="M18" s="5"/>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="5:13">
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="E19" s="5"/>
       <c r="F19" s="1"/>
       <c r="G19" s="2"/>
@@ -1388,7 +1491,7 @@
       <c r="I19" s="2"/>
       <c r="M19" s="5"/>
     </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="5:13">
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="E20" s="5"/>
       <c r="F20" s="1"/>
       <c r="G20" s="2"/>
@@ -1421,7 +1524,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="5"/>
     </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="5:13">
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="E23" s="5"/>
       <c r="F23" s="1"/>
       <c r="G23" s="2"/>
@@ -1444,35 +1547,35 @@
       <c r="L24" s="2"/>
       <c r="M24" s="5"/>
     </row>
-    <row r="25" customHeight="1" spans="12:13">
+    <row r="25" customHeight="1" spans="1:13">
       <c r="L25" s="2"/>
       <c r="M25" s="5"/>
     </row>
-    <row r="26" customHeight="1" spans="12:13">
+    <row r="26" customHeight="1" spans="1:13">
       <c r="L26" s="2"/>
       <c r="M26" s="5"/>
     </row>
-    <row r="27" customHeight="1" spans="12:13">
+    <row r="27" customHeight="1" spans="1:13">
       <c r="L27" s="2"/>
       <c r="M27" s="5"/>
     </row>
-    <row r="28" customHeight="1" spans="12:13">
+    <row r="28" customHeight="1" spans="1:13">
       <c r="L28" s="2"/>
       <c r="M28" s="5"/>
     </row>
-    <row r="29" customHeight="1" spans="12:13">
+    <row r="29" customHeight="1" spans="1:13">
       <c r="L29" s="2"/>
       <c r="M29" s="5"/>
     </row>
-    <row r="30" customHeight="1" spans="12:13">
+    <row r="30" customHeight="1" spans="1:13">
       <c r="L30" s="2"/>
       <c r="M30" s="5"/>
     </row>
-    <row r="31" customHeight="1" spans="12:13">
+    <row r="31" customHeight="1" spans="1:13">
       <c r="L31" s="2"/>
       <c r="M31" s="5"/>
     </row>
-    <row r="32" customHeight="1" spans="12:13">
+    <row r="32" customHeight="1" spans="1:13">
       <c r="L32" s="2"/>
       <c r="M32" s="5"/>
     </row>
